--- a/artfynd/A 6799-2022 artfynd.xlsx
+++ b/artfynd/A 6799-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6799-2022 artfynd.xlsx
+++ b/artfynd/A 6799-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106240128</v>
+        <v>106240127</v>
       </c>
       <c r="B2" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448956.7207945274</v>
+        <v>448992</v>
       </c>
       <c r="R2" t="n">
-        <v>6392697.645090267</v>
+        <v>6392671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +755,9 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106240127</v>
+        <v>106240128</v>
       </c>
       <c r="B3" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448991.752026783</v>
+        <v>448956</v>
       </c>
       <c r="R3" t="n">
-        <v>6392670.995893391</v>
+        <v>6392697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,19 +870,9 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106240109</v>
+        <v>106240129</v>
       </c>
       <c r="B4" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,34 +916,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Granarp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448960.3523867832</v>
+        <v>448978</v>
       </c>
       <c r="R4" t="n">
-        <v>6392645.719573976</v>
+        <v>6392688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,29 +985,25 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1047,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106240136</v>
+        <v>106240130</v>
       </c>
       <c r="B5" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,34 +1031,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6457</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Granarp, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448969.1004929621</v>
+        <v>448978</v>
       </c>
       <c r="R5" t="n">
-        <v>6392659.515129882</v>
+        <v>6392691</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,29 +1100,25 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1159,15 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106240129</v>
+        <v>106240109</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,46 +1146,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Granarp, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448977.4949236466</v>
+        <v>448960</v>
       </c>
       <c r="R6" t="n">
-        <v>6392687.755820315</v>
+        <v>6392645</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,35 +1203,19 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1289,15 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106240130</v>
+        <v>106240135</v>
       </c>
       <c r="B7" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,46 +1243,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Granarp, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448978.6002288255</v>
+        <v>449016</v>
       </c>
       <c r="R7" t="n">
-        <v>6392690.416073118</v>
+        <v>6392684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,35 +1300,19 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1419,15 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106240135</v>
+        <v>106240136</v>
       </c>
       <c r="B8" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449015.4952283873</v>
+        <v>448969</v>
       </c>
       <c r="R8" t="n">
-        <v>6392684.067504719</v>
+        <v>6392660</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,19 +1397,9 @@
           <t>2022-05-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,6 +1423,103 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>66305937</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Granarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>448968</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6392721</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Barnarp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-06-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-06-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6799-2022 artfynd.xlsx
+++ b/artfynd/A 6799-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106240127</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106240128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106240129</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106240130</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106240109</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106240135</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106240136</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,8 +1560,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66305937</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>